--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:24</v>
@@ -2111,7 +2111,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:59</v>
@@ -2681,7 +2681,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:55</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -1199,7 +1199,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:27</v>
@@ -1351,7 +1351,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:43</v>
@@ -1427,7 +1427,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:13</v>
@@ -1465,7 +1465,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>5:48</v>
@@ -1503,7 +1503,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:55</v>
@@ -1769,7 +1769,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:09</v>
@@ -1921,7 +1921,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>5:31</v>
@@ -2073,7 +2073,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:41</v>
@@ -2529,7 +2529,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>5:11</v>
@@ -2567,7 +2567,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>2:55</v>
@@ -2605,7 +2605,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>4:54</v>
@@ -2643,7 +2643,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>5:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:20</v>
+        <v>3:57</v>
       </c>
       <c r="H2" t="str">
-        <v>georgemichael</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:50</v>
+        <v>2:27</v>
       </c>
       <c r="H3" t="str">
-        <v>Cliff Richard</v>
+        <v>070 Shake</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:14</v>
+        <v>4:49</v>
       </c>
       <c r="H4" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:37</v>
+        <v>5:52</v>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v>georgemichael</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -606,10 +606,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:16</v>
+        <v>3:22</v>
       </c>
       <c r="H6" t="str">
-        <v>Alan Walker</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:22</v>
+        <v>4:08</v>
       </c>
       <c r="H7" t="str">
-        <v>The Neighbourhood</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:45</v>
+        <v>7:31</v>
       </c>
       <c r="H8" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Suburban Requiem</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:40</v>
+        <v>3:21</v>
       </c>
       <c r="H9" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:02</v>
+        <v>4:36</v>
       </c>
       <c r="H10" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:12</v>
+        <v>5:06</v>
       </c>
       <c r="H11" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:38</v>
+        <v>4:17</v>
       </c>
       <c r="H12" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:40</v>
+        <v>3:20</v>
       </c>
       <c r="H13" t="str">
-        <v>Cannons</v>
+        <v>georgemichael</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:57</v>
+        <v>4:50</v>
       </c>
       <c r="H14" t="str">
-        <v>Mimi Webb</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:13</v>
+        <v>3:14</v>
       </c>
       <c r="H15" t="str">
-        <v>Jorja Smith</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:12</v>
+        <v>4:37</v>
       </c>
       <c r="H16" t="str">
-        <v>Sam Williams</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:55</v>
+        <v>3:16</v>
       </c>
       <c r="H17" t="str">
-        <v>YUNGBLUD</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:51</v>
+        <v>4:22</v>
       </c>
       <c r="H18" t="str">
-        <v>Megan Moroney</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:51</v>
+        <v>3:45</v>
       </c>
       <c r="H19" t="str">
-        <v>Nico Santos</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:24</v>
+        <v>4:40</v>
       </c>
       <c r="H20" t="str">
-        <v>REALITY CLUB</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:11</v>
+        <v>3:02</v>
       </c>
       <c r="H21" t="str">
-        <v>We Three</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H22" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:06</v>
+        <v>3:38</v>
       </c>
       <c r="H23" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:01</v>
+        <v>4:40</v>
       </c>
       <c r="H24" t="str">
-        <v>Peach PRC</v>
+        <v>Cannons</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>5:38</v>
+        <v>2:57</v>
       </c>
       <c r="H25" t="str">
-        <v>georgemichael</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:43</v>
+        <v>2:13</v>
       </c>
       <c r="H26" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:58</v>
+        <v>4:12</v>
       </c>
       <c r="H27" t="str">
-        <v>Catie Turner</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:13</v>
+        <v>2:55</v>
       </c>
       <c r="H28" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:48</v>
+        <v>3:51</v>
       </c>
       <c r="H29" t="str">
-        <v>U2</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:55</v>
+        <v>2:51</v>
       </c>
       <c r="H30" t="str">
-        <v>Lawrence</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:24</v>
+        <v>3:24</v>
       </c>
       <c r="H31" t="str">
-        <v>BUNT. Music</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:59</v>
+        <v>4:11</v>
       </c>
       <c r="H32" t="str">
-        <v>Bruno Mars</v>
+        <v>We Three</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:10</v>
+        <v>3:27</v>
       </c>
       <c r="H33" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:11</v>
+        <v>3:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:26</v>
+        <v>3:01</v>
       </c>
       <c r="H35" t="str">
-        <v>Neal Francis</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:35</v>
+        <v>5:38</v>
       </c>
       <c r="H36" t="str">
-        <v>mgk</v>
+        <v>georgemichael</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:09</v>
+        <v>3:43</v>
       </c>
       <c r="H37" t="str">
-        <v>Lola Young</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:11</v>
+        <v>2:58</v>
       </c>
       <c r="H38" t="str">
-        <v>Holly Humberstone</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:01</v>
+        <v>4:13</v>
       </c>
       <c r="H39" t="str">
-        <v>The Vaccines</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:28</v>
+        <v>5:48</v>
       </c>
       <c r="H40" t="str">
-        <v>mgk</v>
+        <v>U2</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:31</v>
+        <v>3:55</v>
       </c>
       <c r="H41" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lawrence</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:49</v>
+        <v>5:24</v>
       </c>
       <c r="H42" t="str">
-        <v>Mýa</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:03</v>
+        <v>4:59</v>
       </c>
       <c r="H43" t="str">
-        <v>Michael Bolton</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:59</v>
+        <v>2:10</v>
       </c>
       <c r="H44" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:41</v>
+        <v>3:11</v>
       </c>
       <c r="H45" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:59</v>
+        <v>4:26</v>
       </c>
       <c r="H46" t="str">
-        <v>ENHYPEN</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:59</v>
+        <v>4:35</v>
       </c>
       <c r="H47" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>7:48</v>
+        <v>2:09</v>
       </c>
       <c r="H48" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lola Young</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:10</v>
+        <v>4:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:57</v>
+        <v>3:01</v>
       </c>
       <c r="H50" t="str">
-        <v>The Doobie Brothers</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H51" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,21 +2331,21 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:19</v>
+        <v>5:31</v>
       </c>
       <c r="H52" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:38</v>
+        <v>2:49</v>
       </c>
       <c r="H53" t="str">
-        <v>mgk</v>
+        <v>Mýa</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H54" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:46</v>
+        <v>2:59</v>
       </c>
       <c r="H55" t="str">
-        <v>Jacob Collier</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:25</v>
+        <v>2:41</v>
       </c>
       <c r="H56" t="str">
-        <v>Victor Ray</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:11</v>
+        <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:55</v>
+        <v>3:59</v>
       </c>
       <c r="H58" t="str">
-        <v>The Warning</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:54</v>
+        <v>7:48</v>
       </c>
       <c r="H59" t="str">
-        <v>The Offspring</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:01</v>
+        <v>3:10</v>
       </c>
       <c r="H60" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:55</v>
+        <v>5:57</v>
       </c>
       <c r="H61" t="str">
-        <v>HAUSER</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:43</v>
+        <v>2:25</v>
       </c>
       <c r="H62" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:53</v>
+        <v>3:19</v>
       </c>
       <c r="H63" t="str">
-        <v>Ultra Records</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:30</v>
+        <v>3:38</v>
       </c>
       <c r="H64" t="str">
-        <v>Anja Kotar</v>
+        <v>mgk</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:37</v>
+        <v>4:05</v>
       </c>
       <c r="H65" t="str">
-        <v>Michael Bolton</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:10</v>
+        <v>5:46</v>
       </c>
       <c r="H66" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:06</v>
+        <v>3:25</v>
       </c>
       <c r="H67" t="str">
-        <v>Alan Walker</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:17</v>
+        <v>5:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Bruno Mars</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H69" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>The Warning</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>6:58</v>
+        <v>4:54</v>
       </c>
       <c r="H70" t="str">
-        <v>Eric Church</v>
+        <v>The Offspring</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:29</v>
+        <v>5:01</v>
       </c>
       <c r="H71" t="str">
-        <v>Meghan Trainor</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:14</v>
+        <v>3:55</v>
       </c>
       <c r="H72" t="str">
-        <v>Ally Salort</v>
+        <v>HAUSER</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:51</v>
+        <v>3:43</v>
       </c>
       <c r="H73" t="str">
-        <v>Will Swinton</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:10</v>
+        <v>2:53</v>
       </c>
       <c r="H74" t="str">
-        <v>elijah woods</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:26</v>
+        <v>3:30</v>
       </c>
       <c r="H75" t="str">
-        <v>Jackson Dean</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:51</v>
+        <v>3:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H77" t="str">
-        <v>Neil Sedaka</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3345,7 +3345,7 @@
         <v>3:06</v>
       </c>
       <c r="H78" t="str">
-        <v>Sofia Camara</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:04</v>
+        <v>3:17</v>
       </c>
       <c r="H79" t="str">
-        <v>Russell Dickerson</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H80" t="str">
-        <v>Celine Dion</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:38</v>
+        <v>6:58</v>
       </c>
       <c r="H81" t="str">
-        <v>Bebe Rexha</v>
+        <v>Eric Church</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:29</v>
       </c>
       <c r="H82" t="str">
-        <v>Caroline Jones</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:32</v>
+        <v>3:14</v>
       </c>
       <c r="H83" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:32</v>
+        <v>3:51</v>
       </c>
       <c r="H84" t="str">
-        <v>Ingrid Andress</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:51</v>
+        <v>3:10</v>
       </c>
       <c r="H85" t="str">
-        <v>MusicByKnox</v>
+        <v>elijah woods</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H86" t="str">
-        <v>Ella Langley</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H87" t="str">
-        <v>Nickless</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Caroline Jones</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H89" t="str">
-        <v>elijah woods</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:53</v>
+        <v>3:04</v>
       </c>
       <c r="H90" t="str">
-        <v>August Ponthier</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:10</v>
+        <v>3:03</v>
       </c>
       <c r="H91" t="str">
-        <v>Charli xcx</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:58</v>
+        <v>2:38</v>
       </c>
       <c r="H92" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:44</v>
+        <v>3:29</v>
       </c>
       <c r="H93" t="str">
-        <v>Leah Kate</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:25</v>
+        <v>2:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Troye Sivan</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:08</v>
+        <v>3:32</v>
       </c>
       <c r="H95" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:09</v>
+        <v>2:51</v>
       </c>
       <c r="H96" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:11</v>
+        <v>3:38</v>
       </c>
       <c r="H97" t="str">
-        <v>The Happy Fits</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:02</v>
+        <v>3:26</v>
       </c>
       <c r="H98" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Nickless</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:20</v>
+        <v>3:57</v>
       </c>
       <c r="H99" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:09</v>
+        <v>3:08</v>
       </c>
       <c r="H100" t="str">
-        <v>Quinn XCII</v>
+        <v>elijah woods</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:34</v>
+        <v>3:53</v>
       </c>
       <c r="H101" t="str">
-        <v>We Three</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:57</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="81">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:57</v>
@@ -553,7 +553,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -971,7 +971,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:37</v>
@@ -1009,7 +1009,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:16</v>
@@ -3289,7 +3289,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:10</v>
@@ -3327,7 +3327,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:06</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="81">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:57</v>
@@ -895,7 +895,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:50</v>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:14</v>
@@ -1123,7 +1123,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:40</v>
@@ -3251,7 +3251,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:37</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="81">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -857,7 +857,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:20</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="81">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:57</v>
+        <v>4:39</v>
       </c>
       <c r="H2" t="str">
-        <v>Self Esteem</v>
+        <v>georgemichael</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:27</v>
+        <v>3:40</v>
       </c>
       <c r="H3" t="str">
-        <v>070 Shake</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:49</v>
+        <v>3:57</v>
       </c>
       <c r="H4" t="str">
-        <v>georgemichael</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:52</v>
+        <v>2:27</v>
       </c>
       <c r="H5" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:22</v>
+        <v>4:49</v>
       </c>
       <c r="H6" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:08</v>
+        <v>5:52</v>
       </c>
       <c r="H7" t="str">
-        <v>Romeo Santos</v>
+        <v>georgemichael</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>7:31</v>
+        <v>3:22</v>
       </c>
       <c r="H8" t="str">
-        <v>Jacob Collier</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:21</v>
+        <v>4:08</v>
       </c>
       <c r="H9" t="str">
-        <v>Gabi Sklar</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:36</v>
+        <v>7:31</v>
       </c>
       <c r="H10" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:06</v>
+        <v>3:21</v>
       </c>
       <c r="H11" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:17</v>
+        <v>4:36</v>
       </c>
       <c r="H12" t="str">
-        <v>Marc Anthony</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:20</v>
+        <v>5:06</v>
       </c>
       <c r="H13" t="str">
-        <v>georgemichael</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:50</v>
+        <v>4:17</v>
       </c>
       <c r="H14" t="str">
-        <v>Cliff Richard</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:14</v>
+        <v>3:20</v>
       </c>
       <c r="H15" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:37</v>
+        <v>4:50</v>
       </c>
       <c r="H16" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:16</v>
+        <v>3:14</v>
       </c>
       <c r="H17" t="str">
-        <v>Alan Walker</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:22</v>
+        <v>4:37</v>
       </c>
       <c r="H18" t="str">
-        <v>The Neighbourhood</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:45</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>YUNGBLUD</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Suburban Requiem</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:40</v>
+        <v>4:22</v>
       </c>
       <c r="H20" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-23</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:02</v>
+        <v>3:45</v>
       </c>
       <c r="H21" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:12</v>
+        <v>4:40</v>
       </c>
       <c r="H22" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-23</v>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:38</v>
+        <v>3:02</v>
       </c>
       <c r="H23" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-23</v>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:40</v>
+        <v>3:12</v>
       </c>
       <c r="H24" t="str">
-        <v>Cannons</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-23</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H25" t="str">
-        <v>Mimi Webb</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:13</v>
+        <v>4:40</v>
       </c>
       <c r="H26" t="str">
-        <v>Jorja Smith</v>
+        <v>Cannons</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:12</v>
+        <v>2:57</v>
       </c>
       <c r="H27" t="str">
-        <v>Sam Williams</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:55</v>
+        <v>2:13</v>
       </c>
       <c r="H28" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:51</v>
+        <v>4:12</v>
       </c>
       <c r="H29" t="str">
-        <v>Megan Moroney</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:51</v>
+        <v>2:55</v>
       </c>
       <c r="H30" t="str">
-        <v>Nico Santos</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-23</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:24</v>
+        <v>3:51</v>
       </c>
       <c r="H31" t="str">
-        <v>REALITY CLUB</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-23</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:11</v>
+        <v>2:51</v>
       </c>
       <c r="H32" t="str">
-        <v>We Three</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-23</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:27</v>
+        <v>3:24</v>
       </c>
       <c r="H33" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-23</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:06</v>
+        <v>4:11</v>
       </c>
       <c r="H34" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>We Three</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-23</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:01</v>
+        <v>3:27</v>
       </c>
       <c r="H35" t="str">
-        <v>Peach PRC</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-23</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>5:38</v>
+        <v>3:06</v>
       </c>
       <c r="H36" t="str">
-        <v>georgemichael</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:43</v>
+        <v>3:01</v>
       </c>
       <c r="H37" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-23</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:58</v>
+        <v>5:38</v>
       </c>
       <c r="H38" t="str">
-        <v>Catie Turner</v>
+        <v>georgemichael</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-23</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:13</v>
+        <v>3:43</v>
       </c>
       <c r="H39" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-23</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>5:48</v>
+        <v>2:58</v>
       </c>
       <c r="H40" t="str">
-        <v>U2</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-23</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:55</v>
+        <v>4:13</v>
       </c>
       <c r="H41" t="str">
-        <v>Lawrence</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-23</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>5:24</v>
+        <v>5:48</v>
       </c>
       <c r="H42" t="str">
-        <v>BUNT. Music</v>
+        <v>U2</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-23</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:59</v>
+        <v>3:55</v>
       </c>
       <c r="H43" t="str">
-        <v>Bruno Mars</v>
+        <v>Lawrence</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-23</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:10</v>
+        <v>5:24</v>
       </c>
       <c r="H44" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:11</v>
+        <v>4:59</v>
       </c>
       <c r="H45" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:26</v>
+        <v>2:10</v>
       </c>
       <c r="H46" t="str">
-        <v>Neal Francis</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-23</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:35</v>
+        <v>3:11</v>
       </c>
       <c r="H47" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-23</v>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:09</v>
+        <v>4:26</v>
       </c>
       <c r="H48" t="str">
-        <v>Lola Young</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:11</v>
+        <v>4:35</v>
       </c>
       <c r="H49" t="str">
-        <v>Holly Humberstone</v>
+        <v>mgk</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:01</v>
+        <v>2:09</v>
       </c>
       <c r="H50" t="str">
-        <v>The Vaccines</v>
+        <v>Lola Young</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:28</v>
+        <v>4:11</v>
       </c>
       <c r="H51" t="str">
-        <v>mgk</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:31</v>
+        <v>3:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>3:28</v>
       </c>
       <c r="H53" t="str">
-        <v>Mýa</v>
+        <v>mgk</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-23</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:03</v>
+        <v>5:31</v>
       </c>
       <c r="H54" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-23</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:59</v>
+        <v>2:49</v>
       </c>
       <c r="H55" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Mýa</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H56" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-23</v>
@@ -2547,7 +2547,7 @@
         <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>ENHYPEN</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-23</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:59</v>
+        <v>2:41</v>
       </c>
       <c r="H58" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>7:48</v>
+        <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>The Doobie Brothers</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:10</v>
+        <v>3:59</v>
       </c>
       <c r="H60" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-23</v>
@@ -2696,7 +2696,7 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:57</v>
+        <v>7:48</v>
       </c>
       <c r="H61" t="str">
         <v>The Doobie Brothers</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-23</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:25</v>
+        <v>3:10</v>
       </c>
       <c r="H62" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-23</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:19</v>
+        <v>5:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Michael Bolton</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-23</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:38</v>
+        <v>2:25</v>
       </c>
       <c r="H64" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-23</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:05</v>
+        <v>3:19</v>
       </c>
       <c r="H65" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-23</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:46</v>
+        <v>3:38</v>
       </c>
       <c r="H66" t="str">
-        <v>Jacob Collier</v>
+        <v>mgk</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-23</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:25</v>
+        <v>4:05</v>
       </c>
       <c r="H67" t="str">
-        <v>Victor Ray</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-23</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:11</v>
+        <v>5:46</v>
       </c>
       <c r="H68" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-23</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H69" t="str">
-        <v>The Warning</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-23</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:54</v>
+        <v>5:11</v>
       </c>
       <c r="H70" t="str">
-        <v>The Offspring</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-23</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:01</v>
+        <v>2:55</v>
       </c>
       <c r="H71" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Warning</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-23</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:55</v>
+        <v>4:54</v>
       </c>
       <c r="H72" t="str">
-        <v>HAUSER</v>
+        <v>The Offspring</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-23</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:43</v>
+        <v>5:01</v>
       </c>
       <c r="H73" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:53</v>
+        <v>3:55</v>
       </c>
       <c r="H74" t="str">
-        <v>Ultra Records</v>
+        <v>HAUSER</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-23</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:30</v>
+        <v>3:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Anja Kotar</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:37</v>
+        <v>2:53</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:10</v>
+        <v>3:30</v>
       </c>
       <c r="H77" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-23</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H78" t="str">
-        <v>Alan Walker</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-23</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:17</v>
+        <v>4:10</v>
       </c>
       <c r="H79" t="str">
-        <v>Bruno Mars</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-23</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H80" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-23</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>6:58</v>
+        <v>3:17</v>
       </c>
       <c r="H81" t="str">
-        <v>Eric Church</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-23</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:29</v>
+        <v>3:21</v>
       </c>
       <c r="H82" t="str">
-        <v>Meghan Trainor</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-23</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:14</v>
+        <v>6:58</v>
       </c>
       <c r="H83" t="str">
-        <v>Ally Salort</v>
+        <v>Eric Church</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-23</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:51</v>
+        <v>3:29</v>
       </c>
       <c r="H84" t="str">
-        <v>Will Swinton</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-23</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:10</v>
+        <v>3:14</v>
       </c>
       <c r="H85" t="str">
-        <v>elijah woods</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-23</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H86" t="str">
-        <v>Jackson Dean</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-23</v>
@@ -3684,10 +3684,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:51</v>
+        <v>3:10</v>
       </c>
       <c r="H87" t="str">
-        <v>Matteo Bocelli</v>
+        <v>elijah woods</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B88" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-23</v>
@@ -3725,7 +3725,7 @@
         <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Neil Sedaka</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B89" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-23</v>
@@ -3760,10 +3760,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H89" t="str">
-        <v>Sofia Camara</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-23</v>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:04</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Russell Dickerson</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-23</v>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H91" t="str">
-        <v>Celine Dion</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-23</v>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:38</v>
+        <v>3:04</v>
       </c>
       <c r="H92" t="str">
-        <v>Bebe Rexha</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-23</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:29</v>
+        <v>3:03</v>
       </c>
       <c r="H93" t="str">
-        <v>Caroline Jones</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-23</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:32</v>
+        <v>2:38</v>
       </c>
       <c r="H94" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-23</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:32</v>
+        <v>3:29</v>
       </c>
       <c r="H95" t="str">
-        <v>Ingrid Andress</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-23</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:51</v>
+        <v>2:32</v>
       </c>
       <c r="H96" t="str">
-        <v>MusicByKnox</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-23</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:38</v>
+        <v>3:32</v>
       </c>
       <c r="H97" t="str">
-        <v>Ella Langley</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-23</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H98" t="str">
-        <v>Nickless</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-23</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:57</v>
+        <v>3:38</v>
       </c>
       <c r="H99" t="str">
-        <v>Caroline Jones</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-23</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:08</v>
+        <v>3:26</v>
       </c>
       <c r="H100" t="str">
-        <v>elijah woods</v>
+        <v>Nickless</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-23</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:53</v>
+        <v>3:57</v>
       </c>
       <c r="H101" t="str">
-        <v>August Ponthier</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H2" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H3" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H4" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H5" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H6" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -641,10 +641,10 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H7" t="str">
         <v>georgemichael</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H8" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:08</v>
+        <v>3:22</v>
       </c>
       <c r="H9" t="str">
-        <v>Romeo Santos</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:31</v>
+        <v>4:08</v>
       </c>
       <c r="H10" t="str">
-        <v>Jacob Collier</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:21</v>
+        <v>7:31</v>
       </c>
       <c r="H11" t="str">
-        <v>Gabi Sklar</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:36</v>
+        <v>3:21</v>
       </c>
       <c r="H12" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:06</v>
+        <v>4:36</v>
       </c>
       <c r="H13" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:17</v>
+        <v>5:06</v>
       </c>
       <c r="H14" t="str">
-        <v>Marc Anthony</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:20</v>
+        <v>4:17</v>
       </c>
       <c r="H15" t="str">
-        <v>georgemichael</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:50</v>
+        <v>3:20</v>
       </c>
       <c r="H16" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:14</v>
+        <v>4:50</v>
       </c>
       <c r="H17" t="str">
-        <v>Freya Ridings</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:37</v>
+        <v>3:14</v>
       </c>
       <c r="H18" t="str">
-        <v>Jessie Ware</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>4:37</v>
       </c>
       <c r="H19" t="str">
-        <v>Alan Walker</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-23</v>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:22</v>
+        <v>3:16</v>
       </c>
       <c r="H20" t="str">
-        <v>The Neighbourhood</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-23</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:45</v>
+        <v>4:22</v>
       </c>
       <c r="H21" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Suburban Requiem</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-23</v>
@@ -1211,10 +1211,10 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:40</v>
+        <v>3:45</v>
       </c>
       <c r="H22" t="str">
         <v>YUNGBLUD</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:02</v>
+        <v>4:40</v>
       </c>
       <c r="H23" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-23</v>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H24" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-23</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H25" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:40</v>
+        <v>3:38</v>
       </c>
       <c r="H26" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:57</v>
+        <v>4:40</v>
       </c>
       <c r="H27" t="str">
-        <v>Mimi Webb</v>
+        <v>Cannons</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:13</v>
+        <v>2:57</v>
       </c>
       <c r="H28" t="str">
-        <v>Jorja Smith</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:12</v>
+        <v>2:13</v>
       </c>
       <c r="H29" t="str">
-        <v>Sam Williams</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:55</v>
+        <v>4:12</v>
       </c>
       <c r="H30" t="str">
-        <v>YUNGBLUD</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-23</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H31" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-23</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:51</v>
+        <v>3:51</v>
       </c>
       <c r="H32" t="str">
-        <v>Nico Santos</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-23</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H33" t="str">
-        <v>REALITY CLUB</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-23</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H34" t="str">
-        <v>We Three</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-23</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:27</v>
+        <v>4:11</v>
       </c>
       <c r="H35" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>We Three</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-23</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H36" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H37" t="str">
-        <v>Peach PRC</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-23</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:38</v>
+        <v>3:01</v>
       </c>
       <c r="H38" t="str">
-        <v>georgemichael</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-23</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:43</v>
+        <v>5:38</v>
       </c>
       <c r="H39" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>georgemichael</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-23</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H40" t="str">
-        <v>Catie Turner</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-23</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:13</v>
+        <v>2:58</v>
       </c>
       <c r="H41" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-23</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>5:48</v>
+        <v>4:13</v>
       </c>
       <c r="H42" t="str">
-        <v>U2</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-23</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:55</v>
+        <v>5:48</v>
       </c>
       <c r="H43" t="str">
-        <v>Lawrence</v>
+        <v>U2</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-23</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:24</v>
+        <v>3:55</v>
       </c>
       <c r="H44" t="str">
-        <v>BUNT. Music</v>
+        <v>Lawrence</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B45" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-23</v>
@@ -2088,10 +2088,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:59</v>
+        <v>5:24</v>
       </c>
       <c r="H45" t="str">
-        <v>Bruno Mars</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:10</v>
+        <v>4:59</v>
       </c>
       <c r="H46" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-23</v>
@@ -2164,7 +2164,7 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:11</v>
+        <v>2:10</v>
       </c>
       <c r="H47" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-23</v>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:26</v>
+        <v>3:11</v>
       </c>
       <c r="H48" t="str">
-        <v>Neal Francis</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-23</v>
@@ -2240,10 +2240,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:35</v>
+        <v>4:26</v>
       </c>
       <c r="H49" t="str">
-        <v>mgk</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-23</v>
@@ -2278,10 +2278,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:09</v>
+        <v>4:35</v>
       </c>
       <c r="H50" t="str">
-        <v>Lola Young</v>
+        <v>mgk</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:11</v>
+        <v>2:09</v>
       </c>
       <c r="H51" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lola Young</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:01</v>
+        <v>4:11</v>
       </c>
       <c r="H52" t="str">
-        <v>The Vaccines</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B53" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-23</v>
@@ -2392,10 +2392,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H53" t="str">
-        <v>mgk</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H54" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-23</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H55" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H56" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-23</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H57" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-23</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H58" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-23</v>
@@ -2620,10 +2620,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H59" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-23</v>
@@ -2658,10 +2658,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H60" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-23</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H61" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-23</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H62" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-23</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H63" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-23</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H64" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-23</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H65" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-23</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H66" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-23</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H67" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-23</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H68" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-23</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-23</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H70" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-23</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H71" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-23</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H72" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-23</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H73" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-23</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H74" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-23</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H75" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H76" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H77" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H78" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-23</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H79" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-23</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H80" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-23</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H81" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-23</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H82" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-23</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-23</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H84" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-23</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H85" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-23</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H86" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-23</v>
@@ -3684,10 +3684,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H87" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-23</v>
@@ -3722,10 +3722,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H88" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B89" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-23</v>
@@ -3760,10 +3760,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-23</v>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H90" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-23</v>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-23</v>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H92" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-23</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H93" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-23</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H94" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-23</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H95" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-23</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H96" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-23</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H97" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-23</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H98" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-23</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H99" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-23</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H100" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-23</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H101" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 hour ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 hour ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>5:32</v>
@@ -477,7 +477,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:39</v>
@@ -515,7 +515,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -629,7 +629,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:49</v>
@@ -857,7 +857,7 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:36</v>
@@ -895,7 +895,7 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>5:06</v>
@@ -2073,7 +2073,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>5:24</v>
@@ -2643,7 +2643,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:59</v>
@@ -3175,7 +3175,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>5:01</v>
@@ -3213,7 +3213,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:55</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -436,10 +436,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>5:32</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio) - earMUSIC</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:39</v>
@@ -515,7 +515,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -591,7 +591,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:27</v>
@@ -761,7 +761,7 @@
         <v>4:08</v>
       </c>
       <c r="H10" t="str">
-        <v>Romeo Santos</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="11">
@@ -781,7 +781,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>7:31</v>
@@ -819,7 +819,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:21</v>
@@ -951,7 +951,7 @@
         <v>4:17</v>
       </c>
       <c r="H15" t="str">
-        <v>Marc Anthony</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,7 +963,7 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="16">
@@ -1693,7 +1693,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:11</v>
@@ -1731,7 +1731,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:27</v>
@@ -1883,7 +1883,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:43</v>
@@ -1959,7 +1959,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:13</v>
@@ -1997,7 +1997,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>5:48</v>
@@ -2035,7 +2035,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:55</v>
@@ -2225,7 +2225,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>4:26</v>
@@ -2263,7 +2263,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:35</v>
@@ -2301,7 +2301,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:09</v>
@@ -2339,7 +2339,7 @@
         <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:11</v>
@@ -2415,7 +2415,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:28</v>
@@ -2453,7 +2453,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>5:31</v>
@@ -2529,7 +2529,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:03</v>
@@ -2567,7 +2567,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>2:59</v>
@@ -2605,7 +2605,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:41</v>
@@ -2833,7 +2833,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:25</v>
@@ -2871,7 +2871,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:19</v>
@@ -2909,7 +2909,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:38</v>
@@ -2947,7 +2947,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:05</v>
@@ -2985,7 +2985,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>5:46</v>
@@ -3023,7 +3023,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:25</v>
@@ -3061,7 +3061,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>5:11</v>
@@ -3099,7 +3099,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:55</v>
@@ -3137,7 +3137,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>4:54</v>
@@ -3327,7 +3327,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:30</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
@@ -3547,7 +3547,7 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="84">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>5:32</v>
@@ -477,19 +477,19 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:39</v>
@@ -515,19 +515,19 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:22</v>
@@ -743,19 +743,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>4:08</v>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:17</v>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>4:22</v>
@@ -1199,19 +1199,19 @@
         <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:45</v>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:02</v>
@@ -1313,19 +1313,19 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:12</v>
@@ -1351,19 +1351,19 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:38</v>
@@ -1389,19 +1389,19 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:40</v>
@@ -1427,19 +1427,19 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:57</v>
@@ -1465,19 +1465,19 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:13</v>
@@ -1503,19 +1503,19 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>4:12</v>
@@ -1541,19 +1541,19 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:55</v>
@@ -1579,19 +1579,19 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:51</v>
@@ -1617,19 +1617,19 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:51</v>
@@ -1655,19 +1655,19 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:24</v>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>2:58</v>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:11</v>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:49</v>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>7:48</v>
@@ -2757,19 +2757,19 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:10</v>
@@ -2795,19 +2795,19 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>5:57</v>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:43</v>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:17</v>
@@ -3517,19 +3517,19 @@
         <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:21</v>
@@ -3555,19 +3555,19 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>6:58</v>
@@ -3593,19 +3593,19 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:29</v>
@@ -3631,19 +3631,19 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:14</v>
@@ -3669,19 +3669,19 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>3:51</v>
@@ -3707,19 +3707,19 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:10</v>
@@ -3745,19 +3745,19 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:26</v>
@@ -3783,19 +3783,19 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:51</v>
@@ -3821,19 +3821,19 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B91" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:26</v>
@@ -3859,19 +3859,19 @@
         <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:06</v>
@@ -3897,19 +3897,19 @@
         <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:04</v>
@@ -3935,19 +3935,19 @@
         <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B94" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:03</v>
@@ -3973,19 +3973,19 @@
         <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>2:38</v>
@@ -4011,19 +4011,19 @@
         <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:29</v>
@@ -4049,19 +4049,19 @@
         <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>2:32</v>
@@ -4087,19 +4087,19 @@
         <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:32</v>
@@ -4125,19 +4125,19 @@
         <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>2:51</v>
@@ -4163,19 +4163,19 @@
         <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:38</v>
@@ -4201,19 +4201,19 @@
         <v>Nickless - As I Am</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>5:32</v>
@@ -477,7 +477,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:39</v>
@@ -515,7 +515,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B83" t="str">
         <v>11 days ago</v>
@@ -3547,7 +3547,7 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="84">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>5:32</v>
@@ -477,7 +477,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:39</v>
@@ -515,7 +515,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,7 +553,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:57</v>
@@ -591,7 +591,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:27</v>
@@ -629,7 +629,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:49</v>
@@ -667,7 +667,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>5:52</v>
@@ -781,7 +781,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>7:31</v>
@@ -819,7 +819,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:21</v>
@@ -857,7 +857,7 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:36</v>
@@ -895,7 +895,7 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>5:06</v>
@@ -971,7 +971,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:20</v>
@@ -1009,7 +1009,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:50</v>
@@ -1047,7 +1047,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:14</v>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:37</v>
@@ -1123,7 +1123,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:16</v>
@@ -1237,7 +1237,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:40</v>
@@ -1693,7 +1693,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:11</v>
@@ -1731,7 +1731,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:27</v>
@@ -1769,7 +1769,7 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:06</v>
@@ -1807,7 +1807,7 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:01</v>
@@ -1845,7 +1845,7 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>5:38</v>
@@ -1883,7 +1883,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:43</v>
@@ -1959,7 +1959,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:13</v>
@@ -1997,7 +1997,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>5:48</v>
@@ -2035,7 +2035,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:55</v>
@@ -2073,7 +2073,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>5:24</v>
@@ -2111,7 +2111,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:59</v>
@@ -2149,7 +2149,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:10</v>
@@ -2225,7 +2225,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>4:26</v>
@@ -2263,7 +2263,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:35</v>
@@ -2301,7 +2301,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:09</v>
@@ -2339,7 +2339,7 @@
         <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:11</v>
@@ -2377,7 +2377,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:01</v>
@@ -2415,7 +2415,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:28</v>
@@ -2453,7 +2453,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>5:31</v>
@@ -2529,7 +2529,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:03</v>
@@ -2567,7 +2567,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>2:59</v>
@@ -2605,7 +2605,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:41</v>
@@ -2643,7 +2643,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:59</v>
@@ -2681,7 +2681,7 @@
         <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:59</v>
@@ -2833,7 +2833,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:25</v>
@@ -2871,7 +2871,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:19</v>
@@ -2909,7 +2909,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:38</v>
@@ -2947,7 +2947,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:05</v>
@@ -2985,7 +2985,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>5:46</v>
@@ -3023,7 +3023,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:25</v>
@@ -3061,7 +3061,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>5:11</v>
@@ -3099,7 +3099,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:55</v>
@@ -3137,7 +3137,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>4:54</v>
@@ -3175,7 +3175,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>5:01</v>
@@ -3213,7 +3213,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:55</v>
@@ -3327,7 +3327,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:30</v>
@@ -3365,7 +3365,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:37</v>
@@ -3403,7 +3403,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:10</v>
@@ -3441,7 +3441,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:06</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>11 days ago</v>
@@ -3547,7 +3547,7 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="84">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -1655,7 +1655,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:24</v>
@@ -2187,7 +2187,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:11</v>
@@ -2491,7 +2491,7 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:49</v>
@@ -2795,7 +2795,7 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>5:57</v>
@@ -3251,7 +3251,7 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -933,7 +933,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:17</v>
@@ -1617,7 +1617,7 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:51</v>
@@ -1921,7 +1921,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>2:58</v>
@@ -2757,7 +2757,7 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:22</v>
@@ -743,19 +743,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>4:08</v>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>7:48</v>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -1161,7 +1161,7 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>4:22</v>
@@ -1199,7 +1199,7 @@
         <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:45</v>
@@ -1275,7 +1275,7 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:02</v>
@@ -1313,7 +1313,7 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:12</v>
@@ -1351,7 +1351,7 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:38</v>
@@ -1389,7 +1389,7 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:40</v>
@@ -1427,7 +1427,7 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:57</v>
@@ -1465,7 +1465,7 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:13</v>
@@ -1503,7 +1503,7 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>4:12</v>
@@ -1541,7 +1541,7 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:55</v>
@@ -1579,7 +1579,7 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:51</v>
@@ -3479,7 +3479,7 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:17</v>
@@ -3517,7 +3517,7 @@
         <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:21</v>
@@ -3555,7 +3555,7 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>6:58</v>
@@ -3593,7 +3593,7 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:29</v>
@@ -3631,7 +3631,7 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:14</v>
@@ -3669,7 +3669,7 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>3:51</v>
@@ -3707,7 +3707,7 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:10</v>
@@ -3745,7 +3745,7 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:26</v>
@@ -3783,7 +3783,7 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:51</v>
@@ -3821,7 +3821,7 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:26</v>
@@ -3859,7 +3859,7 @@
         <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:06</v>
@@ -3897,7 +3897,7 @@
         <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:04</v>
@@ -3935,7 +3935,7 @@
         <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:03</v>
@@ -3973,7 +3973,7 @@
         <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>2:38</v>
@@ -4011,7 +4011,7 @@
         <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:29</v>
@@ -4049,7 +4049,7 @@
         <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>2:32</v>
@@ -4087,7 +4087,7 @@
         <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:32</v>
@@ -4125,7 +4125,7 @@
         <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>2:51</v>
@@ -4163,7 +4163,7 @@
         <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:38</v>
@@ -4201,7 +4201,7 @@
         <v>Nickless - As I Am</v>
       </c>
       <c r="B101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:39</v>
@@ -515,7 +515,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -667,7 +667,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>5:52</v>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:37</v>
@@ -1123,7 +1123,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:16</v>
@@ -3403,7 +3403,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:10</v>
@@ -3441,7 +3441,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:06</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -553,7 +553,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:57</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="10">
@@ -1009,7 +1009,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:50</v>
@@ -1047,7 +1047,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:14</v>
@@ -1237,7 +1237,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:40</v>
@@ -3365,7 +3365,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:37</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-25</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>5:32</v>
+        <v>2:28</v>
       </c>
       <c r="H2" t="str">
-        <v>earMUSIC</v>
+        <v>Marcin</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-25</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:39</v>
+        <v>2:47</v>
       </c>
       <c r="H3" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-25</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
       </c>
       <c r="H4" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-25</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:57</v>
+        <v>2:49</v>
       </c>
       <c r="H5" t="str">
-        <v>Self Esteem</v>
+        <v>Ava Max</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-25</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H6" t="str">
-        <v>070 Shake</v>
+        <v>U2</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-25</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H7" t="str">
-        <v>georgemichael</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-25</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:52</v>
+        <v>2:59</v>
       </c>
       <c r="H8" t="str">
-        <v>georgemichael</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-25</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:22</v>
+        <v>4:38</v>
       </c>
       <c r="H9" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-25</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:08</v>
+        <v>3:46</v>
       </c>
       <c r="H10" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-25</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>7:31</v>
+        <v>3:08</v>
       </c>
       <c r="H11" t="str">
-        <v>Jacob Collier</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-25</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:21</v>
+        <v>5:32</v>
       </c>
       <c r="H12" t="str">
-        <v>Gabi Sklar</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-25</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:36</v>
+        <v>4:39</v>
       </c>
       <c r="H13" t="str">
-        <v>YUNGBLUD</v>
+        <v>georgemichael</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-25</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:06</v>
+        <v>3:40</v>
       </c>
       <c r="H14" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-25</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:17</v>
+        <v>3:57</v>
       </c>
       <c r="H15" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-25</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:20</v>
+        <v>2:27</v>
       </c>
       <c r="H16" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-25</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:50</v>
+        <v>4:49</v>
       </c>
       <c r="H17" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-25</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:14</v>
+        <v>5:52</v>
       </c>
       <c r="H18" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-25</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:37</v>
+        <v>3:22</v>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-25</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:16</v>
+        <v>4:08</v>
       </c>
       <c r="H20" t="str">
-        <v>Alan Walker</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-25</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:22</v>
+        <v>7:31</v>
       </c>
       <c r="H21" t="str">
-        <v>The Neighbourhood</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-25</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:45</v>
+        <v>3:21</v>
       </c>
       <c r="H22" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Suburban Requiem</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-25</v>
@@ -1249,10 +1249,10 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:40</v>
+        <v>4:36</v>
       </c>
       <c r="H23" t="str">
         <v>YUNGBLUD</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-25</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:02</v>
+        <v>5:06</v>
       </c>
       <c r="H24" t="str">
-        <v>Calum Scott</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-25</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:12</v>
+        <v>4:17</v>
       </c>
       <c r="H25" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-25</v>
@@ -1366,10 +1366,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:38</v>
+        <v>3:20</v>
       </c>
       <c r="H26" t="str">
-        <v>Dermot Kennedy</v>
+        <v>georgemichael</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-25</v>
@@ -1404,10 +1404,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:40</v>
+        <v>4:50</v>
       </c>
       <c r="H27" t="str">
-        <v>Cannons</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-25</v>
@@ -1442,10 +1442,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H28" t="str">
-        <v>Mimi Webb</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-25</v>
@@ -1480,10 +1480,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:13</v>
+        <v>4:37</v>
       </c>
       <c r="H29" t="str">
-        <v>Jorja Smith</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-25</v>
@@ -1518,10 +1518,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:12</v>
+        <v>3:16</v>
       </c>
       <c r="H30" t="str">
-        <v>Sam Williams</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-25</v>
@@ -1556,10 +1556,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:55</v>
+        <v>4:22</v>
       </c>
       <c r="H31" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-25</v>
@@ -1594,10 +1594,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:51</v>
+        <v>3:45</v>
       </c>
       <c r="H32" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-25</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:51</v>
+        <v>4:40</v>
       </c>
       <c r="H33" t="str">
-        <v>Nico Santos</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-25</v>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:24</v>
+        <v>3:02</v>
       </c>
       <c r="H34" t="str">
-        <v>REALITY CLUB</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-25</v>
@@ -1708,10 +1708,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:11</v>
+        <v>3:12</v>
       </c>
       <c r="H35" t="str">
-        <v>We Three</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-25</v>
@@ -1746,10 +1746,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:27</v>
+        <v>3:38</v>
       </c>
       <c r="H36" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-25</v>
@@ -1784,10 +1784,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:06</v>
+        <v>4:40</v>
       </c>
       <c r="H37" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Cannons</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-25</v>
@@ -1822,10 +1822,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H38" t="str">
-        <v>Peach PRC</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B39" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-25</v>
@@ -1860,10 +1860,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>5:38</v>
+        <v>2:13</v>
       </c>
       <c r="H39" t="str">
-        <v>georgemichael</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-25</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:43</v>
+        <v>4:12</v>
       </c>
       <c r="H40" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-25</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:58</v>
+        <v>2:55</v>
       </c>
       <c r="H41" t="str">
-        <v>Catie Turner</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-25</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:13</v>
+        <v>3:51</v>
       </c>
       <c r="H42" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-25</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>5:48</v>
+        <v>2:51</v>
       </c>
       <c r="H43" t="str">
-        <v>U2</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-25</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:55</v>
+        <v>3:24</v>
       </c>
       <c r="H44" t="str">
-        <v>Lawrence</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-25</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:24</v>
+        <v>4:11</v>
       </c>
       <c r="H45" t="str">
-        <v>BUNT. Music</v>
+        <v>We Three</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-25</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:59</v>
+        <v>3:27</v>
       </c>
       <c r="H46" t="str">
-        <v>Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-25</v>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:10</v>
+        <v>3:06</v>
       </c>
       <c r="H47" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-25</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:11</v>
+        <v>3:01</v>
       </c>
       <c r="H48" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-25</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:26</v>
+        <v>5:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Neal Francis</v>
+        <v>georgemichael</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-25</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:35</v>
+        <v>3:43</v>
       </c>
       <c r="H50" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-25</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:09</v>
+        <v>2:58</v>
       </c>
       <c r="H51" t="str">
-        <v>Lola Young</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-25</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:11</v>
+        <v>4:13</v>
       </c>
       <c r="H52" t="str">
-        <v>Holly Humberstone</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-25</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:01</v>
+        <v>5:48</v>
       </c>
       <c r="H53" t="str">
-        <v>The Vaccines</v>
+        <v>U2</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-25</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:28</v>
+        <v>3:55</v>
       </c>
       <c r="H54" t="str">
-        <v>mgk</v>
+        <v>Lawrence</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-25</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:31</v>
+        <v>5:24</v>
       </c>
       <c r="H55" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-25</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:49</v>
+        <v>4:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Mýa</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-25</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:03</v>
+        <v>2:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-25</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:59</v>
+        <v>3:11</v>
       </c>
       <c r="H58" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-25</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:41</v>
+        <v>4:26</v>
       </c>
       <c r="H59" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-25</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:59</v>
+        <v>4:35</v>
       </c>
       <c r="H60" t="str">
-        <v>ENHYPEN</v>
+        <v>mgk</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-25</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:59</v>
+        <v>2:09</v>
       </c>
       <c r="H61" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lola Young</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-25</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>7:48</v>
+        <v>4:11</v>
       </c>
       <c r="H62" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-25</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:10</v>
+        <v>3:01</v>
       </c>
       <c r="H63" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-25</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>5:57</v>
+        <v>3:28</v>
       </c>
       <c r="H64" t="str">
-        <v>The Doobie Brothers</v>
+        <v>mgk</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-25</v>
@@ -2845,10 +2845,10 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:25</v>
+        <v>5:31</v>
       </c>
       <c r="H65" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-25</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:19</v>
+        <v>2:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-25</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:38</v>
+        <v>3:03</v>
       </c>
       <c r="H67" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-25</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H68" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-25</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:46</v>
+        <v>2:41</v>
       </c>
       <c r="H69" t="str">
-        <v>Jacob Collier</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-25</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:25</v>
+        <v>2:59</v>
       </c>
       <c r="H70" t="str">
-        <v>Victor Ray</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B71" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-25</v>
@@ -3076,10 +3076,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:11</v>
+        <v>3:59</v>
       </c>
       <c r="H71" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B72" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-25</v>
@@ -3114,10 +3114,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:55</v>
+        <v>7:48</v>
       </c>
       <c r="H72" t="str">
-        <v>The Warning</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B73" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-25</v>
@@ -3152,10 +3152,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:54</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>The Offspring</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B74" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-25</v>
@@ -3190,10 +3190,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>5:01</v>
+        <v>5:57</v>
       </c>
       <c r="H74" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-25</v>
@@ -3228,10 +3228,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:55</v>
+        <v>2:25</v>
       </c>
       <c r="H75" t="str">
-        <v>HAUSER</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-25</v>
@@ -3266,10 +3266,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:43</v>
+        <v>3:19</v>
       </c>
       <c r="H76" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-25</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:53</v>
+        <v>3:38</v>
       </c>
       <c r="H77" t="str">
-        <v>Ultra Records</v>
+        <v>mgk</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-25</v>
@@ -3342,10 +3342,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:30</v>
+        <v>4:05</v>
       </c>
       <c r="H78" t="str">
-        <v>Anja Kotar</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-25</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:37</v>
+        <v>5:46</v>
       </c>
       <c r="H79" t="str">
-        <v>Michael Bolton</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-25</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:10</v>
+        <v>3:25</v>
       </c>
       <c r="H80" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-25</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:06</v>
+        <v>5:11</v>
       </c>
       <c r="H81" t="str">
-        <v>Alan Walker</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-25</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:17</v>
+        <v>2:55</v>
       </c>
       <c r="H82" t="str">
-        <v>Bruno Mars</v>
+        <v>The Warning</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-25</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:21</v>
+        <v>4:54</v>
       </c>
       <c r="H83" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>The Offspring</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-25</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>6:58</v>
+        <v>5:01</v>
       </c>
       <c r="H84" t="str">
-        <v>Eric Church</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-25</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H85" t="str">
-        <v>Meghan Trainor</v>
+        <v>HAUSER</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-25</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:14</v>
+        <v>3:43</v>
       </c>
       <c r="H86" t="str">
-        <v>Ally Salort</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-25</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:51</v>
+        <v>2:53</v>
       </c>
       <c r="H87" t="str">
-        <v>Will Swinton</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-25</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H88" t="str">
-        <v>elijah woods</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-25</v>
@@ -3760,10 +3760,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>3:37</v>
       </c>
       <c r="H89" t="str">
-        <v>Jackson Dean</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B90" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-25</v>
@@ -3798,10 +3798,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:51</v>
+        <v>4:10</v>
       </c>
       <c r="H90" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-25</v>
@@ -3836,10 +3836,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H91" t="str">
-        <v>Neil Sedaka</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B92" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-25</v>
@@ -3874,10 +3874,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H92" t="str">
-        <v>Sofia Camara</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-25</v>
@@ -3912,10 +3912,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:04</v>
+        <v>3:21</v>
       </c>
       <c r="H93" t="str">
-        <v>Russell Dickerson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B94" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-25</v>
@@ -3950,10 +3950,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:03</v>
+        <v>6:58</v>
       </c>
       <c r="H94" t="str">
-        <v>Celine Dion</v>
+        <v>Eric Church</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-25</v>
@@ -3988,10 +3988,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H95" t="str">
-        <v>Bebe Rexha</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-25</v>
@@ -4026,10 +4026,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H96" t="str">
-        <v>Caroline Jones</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-25</v>
@@ -4064,10 +4064,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:32</v>
+        <v>3:51</v>
       </c>
       <c r="H97" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-25</v>
@@ -4102,10 +4102,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:32</v>
+        <v>3:10</v>
       </c>
       <c r="H98" t="str">
-        <v>Ingrid Andress</v>
+        <v>elijah woods</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B99" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-25</v>
@@ -4140,10 +4140,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H99" t="str">
-        <v>MusicByKnox</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B100" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-25</v>
@@ -4178,10 +4178,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H100" t="str">
-        <v>Ella Langley</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B101" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-25</v>
@@ -4219,7 +4219,7 @@
         <v>3:26</v>
       </c>
       <c r="H101" t="str">
-        <v>Nickless</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -515,7 +515,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,7 +553,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -667,7 +667,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:59</v>
@@ -1009,7 +1009,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:49</v>
@@ -2453,7 +2453,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>5:24</v>
@@ -3023,7 +3023,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>2:59</v>
@@ -3593,7 +3593,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:55</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -515,7 +515,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,7 +553,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -705,7 +705,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:38</v>
@@ -743,7 +743,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:08</v>
@@ -971,7 +971,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:27</v>
@@ -1161,7 +1161,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>7:31</v>
@@ -1199,7 +1199,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:21</v>
@@ -1237,7 +1237,7 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:36</v>
@@ -1275,7 +1275,7 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>5:06</v>
@@ -2073,7 +2073,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>4:11</v>
@@ -2111,7 +2111,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:27</v>
@@ -2263,7 +2263,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:43</v>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:13</v>
@@ -2377,7 +2377,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>5:48</v>
@@ -2415,7 +2415,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:55</v>
@@ -2643,7 +2643,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>4:35</v>
@@ -2681,7 +2681,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:09</v>
@@ -2719,7 +2719,7 @@
         <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:11</v>
@@ -2795,7 +2795,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:28</v>
@@ -2833,7 +2833,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>5:31</v>
@@ -2909,7 +2909,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:03</v>
@@ -2947,7 +2947,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>2:59</v>
@@ -2985,7 +2985,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:41</v>
@@ -3213,7 +3213,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:25</v>
@@ -3251,7 +3251,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:19</v>
@@ -3289,7 +3289,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:38</v>
@@ -3327,7 +3327,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:05</v>
@@ -3365,7 +3365,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>5:46</v>
@@ -3403,7 +3403,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:25</v>
@@ -3441,7 +3441,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>5:11</v>
@@ -3479,7 +3479,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>2:55</v>
@@ -3517,7 +3517,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:54</v>
@@ -3555,7 +3555,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>5:01</v>
@@ -3707,7 +3707,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:30</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -515,7 +515,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,7 +553,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -629,7 +629,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:35</v>
@@ -2605,7 +2605,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>4:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -515,7 +515,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,7 +553,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -1313,7 +1313,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>4:17</v>
@@ -1997,7 +1997,7 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:51</v>
@@ -2035,7 +2035,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:24</v>
@@ -2301,7 +2301,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:58</v>
@@ -2567,7 +2567,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:11</v>
@@ -2871,7 +2871,7 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:49</v>
@@ -3137,7 +3137,7 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:10</v>
@@ -3175,7 +3175,7 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>5:57</v>
@@ -3631,7 +3631,7 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -477,19 +477,19 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -515,19 +515,19 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,19 +553,19 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:22</v>
@@ -1123,19 +1123,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:08</v>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>4:22</v>
@@ -1579,19 +1579,19 @@
         <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:45</v>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:02</v>
@@ -1693,19 +1693,19 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:12</v>
@@ -1731,19 +1731,19 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:38</v>
@@ -1769,19 +1769,19 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:40</v>
@@ -1807,19 +1807,19 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:57</v>
@@ -1845,19 +1845,19 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:13</v>
@@ -1883,19 +1883,19 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:12</v>
@@ -1921,19 +1921,19 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>2:55</v>
@@ -1959,19 +1959,19 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:51</v>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>7:48</v>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:17</v>
@@ -3897,19 +3897,19 @@
         <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:21</v>
@@ -3935,19 +3935,19 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>6:58</v>
@@ -3973,19 +3973,19 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>3:29</v>
@@ -4011,19 +4011,19 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:14</v>
@@ -4049,19 +4049,19 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:51</v>
@@ -4087,19 +4087,19 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:10</v>
@@ -4125,19 +4125,19 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B99" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:26</v>
@@ -4163,19 +4163,19 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B100" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>2:51</v>
@@ -4201,19 +4201,19 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B101" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -857,7 +857,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:39</v>
@@ -895,7 +895,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:40</v>
@@ -1047,7 +1047,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>5:52</v>
@@ -1389,7 +1389,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:50</v>
@@ -1427,7 +1427,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:14</v>
@@ -1465,7 +1465,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:37</v>
@@ -1503,7 +1503,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:16</v>
@@ -3745,7 +3745,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:37</v>
@@ -3783,7 +3783,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>4:10</v>
@@ -3821,7 +3821,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:06</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -591,7 +591,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:49</v>
@@ -819,7 +819,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>5:32</v>
@@ -933,7 +933,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:57</v>
@@ -1351,7 +1351,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:20</v>
@@ -1617,7 +1617,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:40</v>
@@ -2225,7 +2225,7 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>5:38</v>
@@ -2757,7 +2757,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -667,7 +667,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:59</v>
@@ -1009,7 +1009,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:49</v>
@@ -2149,7 +2149,7 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:06</v>
@@ -2187,7 +2187,7 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:01</v>
@@ -2453,7 +2453,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>5:24</v>
@@ -2491,7 +2491,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>4:59</v>
@@ -2529,7 +2529,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>2:10</v>
@@ -3023,7 +3023,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>2:59</v>
@@ -3061,7 +3061,7 @@
         <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:59</v>
@@ -3593,7 +3593,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:55</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -629,7 +629,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:35</v>
@@ -705,7 +705,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:38</v>
@@ -743,7 +743,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:08</v>
@@ -971,7 +971,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:27</v>
@@ -1161,7 +1161,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>7:31</v>
@@ -1199,7 +1199,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:21</v>
@@ -1237,7 +1237,7 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:36</v>
@@ -1275,7 +1275,7 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>5:06</v>
@@ -2035,7 +2035,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:24</v>
@@ -2073,7 +2073,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>4:11</v>
@@ -2111,7 +2111,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:27</v>
@@ -2263,7 +2263,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:43</v>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:13</v>
@@ -2377,7 +2377,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>5:48</v>
@@ -2415,7 +2415,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:55</v>
@@ -2567,7 +2567,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:11</v>
@@ -2605,7 +2605,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>4:26</v>
@@ -2643,7 +2643,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>4:35</v>
@@ -2681,7 +2681,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:09</v>
@@ -2719,7 +2719,7 @@
         <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:11</v>
@@ -2795,7 +2795,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:28</v>
@@ -2833,7 +2833,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>5:31</v>
@@ -2871,7 +2871,7 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:49</v>
@@ -2909,7 +2909,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:03</v>
@@ -2947,7 +2947,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>2:59</v>
@@ -2985,7 +2985,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:41</v>
@@ -3175,7 +3175,7 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>5:57</v>
@@ -3213,7 +3213,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:25</v>
@@ -3251,7 +3251,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:19</v>
@@ -3289,7 +3289,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:38</v>
@@ -3327,7 +3327,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:05</v>
@@ -3365,7 +3365,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>5:46</v>
@@ -3403,7 +3403,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:25</v>
@@ -3441,7 +3441,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>5:11</v>
@@ -3479,7 +3479,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>2:55</v>
@@ -3517,7 +3517,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:54</v>
@@ -3555,7 +3555,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>5:01</v>
@@ -3631,7 +3631,7 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:43</v>
@@ -3707,7 +3707,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:30</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -515,19 +515,19 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,19 +553,19 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -591,19 +591,19 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:49</v>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:39</v>
@@ -895,19 +895,19 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:40</v>
@@ -933,19 +933,19 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:57</v>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>5:52</v>
@@ -1085,19 +1085,19 @@
         <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:22</v>
@@ -1123,19 +1123,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:08</v>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>4:17</v>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:50</v>
@@ -1427,19 +1427,19 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:14</v>
@@ -1465,19 +1465,19 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:37</v>
@@ -1503,19 +1503,19 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:16</v>
@@ -1541,19 +1541,19 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>4:22</v>
@@ -1579,19 +1579,19 @@
         <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:45</v>
@@ -1617,19 +1617,19 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:40</v>
@@ -1655,19 +1655,19 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:02</v>
@@ -1693,19 +1693,19 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:12</v>
@@ -1731,19 +1731,19 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:38</v>
@@ -1769,19 +1769,19 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:40</v>
@@ -1807,19 +1807,19 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:57</v>
@@ -1845,19 +1845,19 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:13</v>
@@ -1883,19 +1883,19 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:12</v>
@@ -1921,19 +1921,19 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>2:55</v>
@@ -1959,19 +1959,19 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:51</v>
@@ -1997,19 +1997,19 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:51</v>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:58</v>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>7:48</v>
@@ -3137,19 +3137,19 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:10</v>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:37</v>
@@ -3783,19 +3783,19 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v>4:10</v>
@@ -3821,19 +3821,19 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:06</v>
@@ -3859,19 +3859,19 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:17</v>
@@ -3894,22 +3894,22 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:21</v>
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="94">
@@ -3935,19 +3935,19 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v>6:58</v>
@@ -3973,19 +3973,19 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v>3:29</v>
@@ -4011,19 +4011,19 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:14</v>
@@ -4049,19 +4049,19 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:51</v>
@@ -4087,19 +4087,19 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:10</v>
@@ -4125,19 +4125,19 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:26</v>
@@ -4163,19 +4163,19 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>2:51</v>
@@ -4201,19 +4201,19 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B101" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:35</v>
@@ -667,19 +667,19 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:59</v>
@@ -705,19 +705,19 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:38</v>
@@ -743,19 +743,19 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,19 +781,19 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:08</v>
@@ -819,19 +819,19 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>5:32</v>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:27</v>
@@ -1009,19 +1009,19 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:49</v>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:22</v>
@@ -1123,19 +1123,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:08</v>
@@ -1161,19 +1161,19 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>7:31</v>
@@ -1199,19 +1199,19 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:21</v>
@@ -1237,19 +1237,19 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:36</v>
@@ -1275,19 +1275,19 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>5:06</v>
@@ -1313,19 +1313,19 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>4:17</v>
@@ -1351,19 +1351,19 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:20</v>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:51</v>
@@ -2035,19 +2035,19 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:24</v>
@@ -2073,19 +2073,19 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>4:11</v>
@@ -2111,19 +2111,19 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:27</v>
@@ -2149,19 +2149,19 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:06</v>
@@ -2187,19 +2187,19 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:01</v>
@@ -2225,19 +2225,19 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>5:38</v>
@@ -2263,19 +2263,19 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:43</v>
@@ -2301,19 +2301,19 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:58</v>
@@ -2339,19 +2339,19 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:13</v>
@@ -2377,19 +2377,19 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>5:48</v>
@@ -2415,19 +2415,19 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:55</v>
@@ -2453,19 +2453,19 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>5:24</v>
@@ -2491,19 +2491,19 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>4:59</v>
@@ -2529,19 +2529,19 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>2:10</v>
@@ -2567,19 +2567,19 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:11</v>
@@ -2605,19 +2605,19 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>4:26</v>
@@ -2643,19 +2643,19 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>4:35</v>
@@ -2681,19 +2681,19 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:09</v>
@@ -2719,19 +2719,19 @@
         <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:11</v>
@@ -2757,19 +2757,19 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:01</v>
@@ -2795,19 +2795,19 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:28</v>
@@ -2833,19 +2833,19 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>5:31</v>
@@ -2871,19 +2871,19 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:49</v>
@@ -2909,19 +2909,19 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:03</v>
@@ -2947,19 +2947,19 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>2:59</v>
@@ -2985,19 +2985,19 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:41</v>
@@ -3023,19 +3023,19 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>2:59</v>
@@ -3061,19 +3061,19 @@
         <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:59</v>
@@ -3099,19 +3099,19 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v>7:48</v>
@@ -3137,19 +3137,19 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:10</v>
@@ -3175,19 +3175,19 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v>5:57</v>
@@ -3213,19 +3213,19 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:25</v>
@@ -3251,19 +3251,19 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:19</v>
@@ -3289,19 +3289,19 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:38</v>
@@ -3327,19 +3327,19 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:05</v>
@@ -3365,19 +3365,19 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v>5:46</v>
@@ -3403,19 +3403,19 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:25</v>
@@ -3441,19 +3441,19 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v>5:11</v>
@@ -3479,19 +3479,19 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v>2:55</v>
@@ -3517,19 +3517,19 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:54</v>
@@ -3555,19 +3555,19 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>5:01</v>
@@ -3593,19 +3593,19 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:55</v>
@@ -3631,19 +3631,19 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:43</v>
@@ -3669,19 +3669,19 @@
         <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v>2:53</v>
@@ -3707,19 +3707,19 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:30</v>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="94">
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:40</v>
@@ -553,7 +553,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -1541,7 +1541,7 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>4:22</v>
@@ -1579,7 +1579,7 @@
         <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:45</v>
@@ -1655,7 +1655,7 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:02</v>
@@ -1693,7 +1693,7 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:12</v>
@@ -1731,7 +1731,7 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:38</v>
@@ -1769,7 +1769,7 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:40</v>
@@ -1807,7 +1807,7 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:57</v>
@@ -1845,7 +1845,7 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:13</v>
@@ -1883,7 +1883,7 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:12</v>
@@ -1921,7 +1921,7 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>2:55</v>
@@ -1959,7 +1959,7 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:47</v>
@@ -857,7 +857,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:39</v>
@@ -895,7 +895,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:40</v>
@@ -1047,7 +1047,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>5:52</v>
@@ -1465,7 +1465,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:37</v>
@@ -1503,7 +1503,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:28</v>
@@ -591,7 +591,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:49</v>
@@ -933,7 +933,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:57</v>
@@ -1351,7 +1351,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:20</v>
@@ -1389,7 +1389,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:50</v>
@@ -1427,7 +1427,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:14</v>
@@ -1617,7 +1617,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:40</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-28</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v>2:28</v>
+        <v>2:46</v>
       </c>
       <c r="H2" t="str">
-        <v>Marcin</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-28</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:47</v>
+        <v>2:42</v>
       </c>
       <c r="H3" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-28</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H4" t="str">
-        <v>Laufey</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-28</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:49</v>
+        <v>2:59</v>
       </c>
       <c r="H5" t="str">
-        <v>Ava Max</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-28</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:49</v>
+        <v>2:22</v>
       </c>
       <c r="H6" t="str">
-        <v>U2</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-28</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:35</v>
+        <v>3:53</v>
       </c>
       <c r="H7" t="str">
-        <v>Taylor Swift</v>
+        <v>Roxette</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-28</v>
@@ -682,10 +682,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:59</v>
+        <v>2:28</v>
       </c>
       <c r="H8" t="str">
-        <v>Kiana Ledé</v>
+        <v>Marcin</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-28</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:38</v>
+        <v>2:47</v>
       </c>
       <c r="H9" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-28</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:46</v>
+        <v>3:40</v>
       </c>
       <c r="H10" t="str">
-        <v>Madison Beer</v>
+        <v>Laufey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-28</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H11" t="str">
-        <v>Sean Stemaly</v>
+        <v>Ava Max</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B12" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-28</v>
@@ -834,10 +834,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:32</v>
+        <v>4:49</v>
       </c>
       <c r="H12" t="str">
-        <v>earMUSIC</v>
+        <v>U2</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-28</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:39</v>
+        <v>3:35</v>
       </c>
       <c r="H13" t="str">
-        <v>georgemichael</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-28</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:40</v>
+        <v>2:59</v>
       </c>
       <c r="H14" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-28</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:57</v>
+        <v>4:38</v>
       </c>
       <c r="H15" t="str">
-        <v>Self Esteem</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-28</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:27</v>
+        <v>3:46</v>
       </c>
       <c r="H16" t="str">
-        <v>070 Shake</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-28</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:49</v>
+        <v>3:08</v>
       </c>
       <c r="H17" t="str">
-        <v>georgemichael</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-28</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:52</v>
+        <v>5:32</v>
       </c>
       <c r="H18" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-28</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:22</v>
+        <v>4:39</v>
       </c>
       <c r="H19" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-28</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:08</v>
+        <v>3:40</v>
       </c>
       <c r="H20" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-28</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>7:31</v>
+        <v>3:57</v>
       </c>
       <c r="H21" t="str">
-        <v>Jacob Collier</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-28</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:21</v>
+        <v>2:27</v>
       </c>
       <c r="H22" t="str">
-        <v>Gabi Sklar</v>
+        <v>070 Shake</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B23" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-28</v>
@@ -1252,10 +1252,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:36</v>
+        <v>4:49</v>
       </c>
       <c r="H23" t="str">
-        <v>YUNGBLUD</v>
+        <v>georgemichael</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B24" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-28</v>
@@ -1290,10 +1290,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>5:06</v>
+        <v>5:52</v>
       </c>
       <c r="H24" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>georgemichael</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B25" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-28</v>
@@ -1328,10 +1328,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:17</v>
+        <v>3:22</v>
       </c>
       <c r="H25" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-28</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:20</v>
+        <v>4:08</v>
       </c>
       <c r="H26" t="str">
-        <v>georgemichael</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-28</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:50</v>
+        <v>7:31</v>
       </c>
       <c r="H27" t="str">
-        <v>Cliff Richard</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-28</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H28" t="str">
-        <v>Freya Ridings</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-28</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:37</v>
+        <v>4:36</v>
       </c>
       <c r="H29" t="str">
-        <v>Jessie Ware</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-28</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:16</v>
+        <v>5:06</v>
       </c>
       <c r="H30" t="str">
-        <v>Alan Walker</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-28</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:22</v>
+        <v>4:17</v>
       </c>
       <c r="H31" t="str">
-        <v>The Neighbourhood</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B32" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-28</v>
@@ -1594,10 +1594,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:45</v>
+        <v>3:20</v>
       </c>
       <c r="H32" t="str">
-        <v>YUNGBLUD</v>
+        <v>georgemichael</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Suburban Requiem</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-28</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:40</v>
+        <v>4:50</v>
       </c>
       <c r="H33" t="str">
-        <v>YUNGBLUD</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-28</v>
@@ -1670,10 +1670,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H34" t="str">
-        <v>Calum Scott</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B35" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-28</v>
@@ -1708,10 +1708,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:12</v>
+        <v>4:37</v>
       </c>
       <c r="H35" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B36" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-28</v>
@@ -1746,10 +1746,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:38</v>
+        <v>3:16</v>
       </c>
       <c r="H36" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-28</v>
@@ -1784,10 +1784,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:40</v>
+        <v>4:22</v>
       </c>
       <c r="H37" t="str">
-        <v>Cannons</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-28</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:57</v>
+        <v>4:40</v>
       </c>
       <c r="H38" t="str">
-        <v>Mimi Webb</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-28</v>
@@ -1860,10 +1860,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:13</v>
+        <v>3:02</v>
       </c>
       <c r="H39" t="str">
-        <v>Jorja Smith</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-28</v>
@@ -1898,10 +1898,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:12</v>
+        <v>3:12</v>
       </c>
       <c r="H40" t="str">
-        <v>Sam Williams</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B41" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-28</v>
@@ -1936,10 +1936,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:55</v>
+        <v>3:38</v>
       </c>
       <c r="H41" t="str">
-        <v>YUNGBLUD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B42" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-28</v>
@@ -1974,10 +1974,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:51</v>
+        <v>4:40</v>
       </c>
       <c r="H42" t="str">
-        <v>Megan Moroney</v>
+        <v>Cannons</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-28</v>
@@ -2012,10 +2012,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:51</v>
+        <v>2:57</v>
       </c>
       <c r="H43" t="str">
-        <v>Nico Santos</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B44" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-28</v>
@@ -2050,10 +2050,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:24</v>
+        <v>2:13</v>
       </c>
       <c r="H44" t="str">
-        <v>REALITY CLUB</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-28</v>
@@ -2088,10 +2088,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:11</v>
+        <v>4:12</v>
       </c>
       <c r="H45" t="str">
-        <v>We Three</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-28</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:27</v>
+        <v>2:55</v>
       </c>
       <c r="H46" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-28</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:06</v>
+        <v>3:51</v>
       </c>
       <c r="H47" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-28</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:01</v>
+        <v>2:51</v>
       </c>
       <c r="H48" t="str">
-        <v>Peach PRC</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-28</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:38</v>
+        <v>3:24</v>
       </c>
       <c r="H49" t="str">
-        <v>georgemichael</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-28</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:43</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>We Three</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-28</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:58</v>
+        <v>3:27</v>
       </c>
       <c r="H51" t="str">
-        <v>Catie Turner</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B52" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-28</v>
@@ -2354,10 +2354,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:13</v>
+        <v>3:06</v>
       </c>
       <c r="H52" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B53" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-28</v>
@@ -2392,10 +2392,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>5:48</v>
+        <v>3:01</v>
       </c>
       <c r="H53" t="str">
-        <v>U2</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B54" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-28</v>
@@ -2430,10 +2430,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:55</v>
+        <v>5:38</v>
       </c>
       <c r="H54" t="str">
-        <v>Lawrence</v>
+        <v>georgemichael</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-28</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:24</v>
+        <v>3:43</v>
       </c>
       <c r="H55" t="str">
-        <v>BUNT. Music</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-28</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:59</v>
+        <v>2:58</v>
       </c>
       <c r="H56" t="str">
-        <v>Bruno Mars</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-28</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:10</v>
+        <v>4:13</v>
       </c>
       <c r="H57" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-28</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:11</v>
+        <v>5:48</v>
       </c>
       <c r="H58" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>U2</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-28</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:26</v>
+        <v>3:55</v>
       </c>
       <c r="H59" t="str">
-        <v>Neal Francis</v>
+        <v>Lawrence</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B60" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-28</v>
@@ -2658,10 +2658,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:35</v>
+        <v>5:24</v>
       </c>
       <c r="H60" t="str">
-        <v>mgk</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B61" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-28</v>
@@ -2696,10 +2696,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:09</v>
+        <v>4:59</v>
       </c>
       <c r="H61" t="str">
-        <v>Lola Young</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-28</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:11</v>
+        <v>2:10</v>
       </c>
       <c r="H62" t="str">
-        <v>Holly Humberstone</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-28</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:01</v>
+        <v>3:11</v>
       </c>
       <c r="H63" t="str">
-        <v>The Vaccines</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-28</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:28</v>
+        <v>4:26</v>
       </c>
       <c r="H64" t="str">
-        <v>mgk</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-28</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:31</v>
+        <v>4:35</v>
       </c>
       <c r="H65" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-28</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:49</v>
+        <v>2:09</v>
       </c>
       <c r="H66" t="str">
-        <v>Mýa</v>
+        <v>Lola Young</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-28</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:03</v>
+        <v>4:11</v>
       </c>
       <c r="H67" t="str">
-        <v>Michael Bolton</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-28</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:59</v>
+        <v>3:01</v>
       </c>
       <c r="H68" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-28</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:41</v>
+        <v>3:28</v>
       </c>
       <c r="H69" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>mgk</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B70" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-28</v>
@@ -3038,10 +3038,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:59</v>
+        <v>5:31</v>
       </c>
       <c r="H70" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-28</v>
@@ -3076,10 +3076,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H71" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mýa</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-28</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>7:48</v>
+        <v>3:03</v>
       </c>
       <c r="H72" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-28</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:59</v>
       </c>
       <c r="H73" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-28</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>5:57</v>
+        <v>2:41</v>
       </c>
       <c r="H74" t="str">
-        <v>The Doobie Brothers</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-28</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H75" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-28</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:19</v>
+        <v>3:59</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-28</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:38</v>
+        <v>7:48</v>
       </c>
       <c r="H77" t="str">
-        <v>mgk</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-28</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:05</v>
+        <v>3:10</v>
       </c>
       <c r="H78" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-28</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>5:46</v>
+        <v>5:57</v>
       </c>
       <c r="H79" t="str">
-        <v>Jacob Collier</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-28</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:25</v>
+        <v>2:25</v>
       </c>
       <c r="H80" t="str">
-        <v>Victor Ray</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-28</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>5:11</v>
+        <v>3:19</v>
       </c>
       <c r="H81" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-28</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:55</v>
+        <v>3:38</v>
       </c>
       <c r="H82" t="str">
-        <v>The Warning</v>
+        <v>mgk</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-28</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:54</v>
+        <v>4:05</v>
       </c>
       <c r="H83" t="str">
-        <v>The Offspring</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-28</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>5:01</v>
+        <v>5:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-28</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:55</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>HAUSER</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-28</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:43</v>
+        <v>5:11</v>
       </c>
       <c r="H86" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-28</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:53</v>
+        <v>2:55</v>
       </c>
       <c r="H87" t="str">
-        <v>Ultra Records</v>
+        <v>The Warning</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-28</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:30</v>
+        <v>4:54</v>
       </c>
       <c r="H88" t="str">
-        <v>Anja Kotar</v>
+        <v>The Offspring</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-28</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:37</v>
+        <v>5:01</v>
       </c>
       <c r="H89" t="str">
-        <v>Michael Bolton</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-28</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:10</v>
+        <v>3:55</v>
       </c>
       <c r="H90" t="str">
-        <v>Nothing But Thieves</v>
+        <v>HAUSER</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-28</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:06</v>
+        <v>3:43</v>
       </c>
       <c r="H91" t="str">
-        <v>Alan Walker</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-28</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H92" t="str">
-        <v>Bruno Mars</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-28</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:21</v>
+        <v>3:30</v>
       </c>
       <c r="H93" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-28</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>6:58</v>
+        <v>3:37</v>
       </c>
       <c r="H94" t="str">
-        <v>Eric Church</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-28</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:29</v>
+        <v>4:10</v>
       </c>
       <c r="H95" t="str">
-        <v>Meghan Trainor</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-28</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:14</v>
+        <v>3:06</v>
       </c>
       <c r="H96" t="str">
-        <v>Ally Salort</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-28</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H97" t="str">
-        <v>Will Swinton</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-28</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H98" t="str">
-        <v>elijah woods</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-28</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:26</v>
+        <v>6:58</v>
       </c>
       <c r="H99" t="str">
-        <v>Jackson Dean</v>
+        <v>Eric Church</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-28</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H100" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-28</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H101" t="str">
-        <v>Neil Sedaka</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-28</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>2:46</v>
+        <v>3:11</v>
       </c>
       <c r="H2" t="str">
-        <v>Bryan Ferry</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-28</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:42</v>
+        <v>3:32</v>
       </c>
       <c r="H3" t="str">
-        <v>Saint Harison</v>
+        <v>Lauv</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-28</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:04</v>
+        <v>5:03</v>
       </c>
       <c r="H4" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>RAYE</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-28</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:59</v>
+        <v>4:50</v>
       </c>
       <c r="H5" t="str">
-        <v>Catie Turner</v>
+        <v>Armik</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-28</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:22</v>
+        <v>4:53</v>
       </c>
       <c r="H6" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Scorpions</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-28</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:53</v>
+        <v>3:04</v>
       </c>
       <c r="H7" t="str">
-        <v>Roxette</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-28</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:28</v>
+        <v>4:32</v>
       </c>
       <c r="H8" t="str">
-        <v>Marcin</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-28</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:47</v>
+        <v>3:47</v>
       </c>
       <c r="H9" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-28</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:40</v>
       </c>
       <c r="H10" t="str">
-        <v>Laufey</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-28</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:49</v>
+        <v>4:05</v>
       </c>
       <c r="H11" t="str">
-        <v>Ava Max</v>
+        <v>HAUSER</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-28</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:49</v>
+        <v>2:59</v>
       </c>
       <c r="H12" t="str">
-        <v>U2</v>
+        <v>Queen Official</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-28</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:35</v>
+        <v>3:55</v>
       </c>
       <c r="H13" t="str">
-        <v>Taylor Swift</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-28</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:59</v>
+        <v>5:12</v>
       </c>
       <c r="H14" t="str">
-        <v>Kiana Ledé</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-28</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:38</v>
+        <v>3:47</v>
       </c>
       <c r="H15" t="str">
-        <v>Jessie Ware</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-28</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:46</v>
+        <v>3:18</v>
       </c>
       <c r="H16" t="str">
-        <v>Madison Beer</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-28</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:08</v>
+        <v>3:50</v>
       </c>
       <c r="H17" t="str">
-        <v>Sean Stemaly</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-28</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:32</v>
+        <v>3:24</v>
       </c>
       <c r="H18" t="str">
-        <v>earMUSIC</v>
+        <v>MyKey</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-28</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:39</v>
+        <v>2:36</v>
       </c>
       <c r="H19" t="str">
-        <v>georgemichael</v>
+        <v>Max McNown</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-28</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:40</v>
+        <v>3:34</v>
       </c>
       <c r="H20" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-28</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:57</v>
+        <v>4:03</v>
       </c>
       <c r="H21" t="str">
-        <v>Self Esteem</v>
+        <v>ERNEST</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-28</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:27</v>
+        <v>3:31</v>
       </c>
       <c r="H22" t="str">
-        <v>070 Shake</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-28</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:49</v>
+        <v>3:22</v>
       </c>
       <c r="H23" t="str">
-        <v>georgemichael</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-28</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
-        <v>5:52</v>
+        <v>5:49</v>
       </c>
       <c r="H24" t="str">
-        <v>georgemichael</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-28</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:22</v>
+        <v>3:47</v>
       </c>
       <c r="H25" t="str">
-        <v>Foo Fighters</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-28</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:08</v>
+        <v>2:20</v>
       </c>
       <c r="H26" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-28</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
-        <v>7:31</v>
+        <v>4:18</v>
       </c>
       <c r="H27" t="str">
-        <v>Jacob Collier</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-28</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:21</v>
+        <v>2:39</v>
       </c>
       <c r="H28" t="str">
-        <v>Gabi Sklar</v>
+        <v>kenzie</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-28</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:36</v>
+        <v>3:52</v>
       </c>
       <c r="H29" t="str">
-        <v>YUNGBLUD</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-28</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
-        <v>5:06</v>
+        <v>4:01</v>
       </c>
       <c r="H30" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-28</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:17</v>
+        <v>2:54</v>
       </c>
       <c r="H31" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>CHESCA</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-28</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:20</v>
+        <v>4:03</v>
       </c>
       <c r="H32" t="str">
-        <v>georgemichael</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-28</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:50</v>
       </c>
       <c r="H33" t="str">
-        <v>Cliff Richard</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-28</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:14</v>
+        <v>3:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Freya Ridings</v>
+        <v>Y2K</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-28</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:37</v>
+        <v>2:43</v>
       </c>
       <c r="H35" t="str">
-        <v>Jessie Ware</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-28</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:16</v>
+        <v>6:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Alan Walker</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-28</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:22</v>
+        <v>2:46</v>
       </c>
       <c r="H37" t="str">
-        <v>The Neighbourhood</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Suburban Requiem</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-28</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:40</v>
+        <v>2:42</v>
       </c>
       <c r="H38" t="str">
-        <v>YUNGBLUD</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-28</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:02</v>
+        <v>3:04</v>
       </c>
       <c r="H39" t="str">
-        <v>Calum Scott</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-28</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:12</v>
+        <v>2:59</v>
       </c>
       <c r="H40" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-28</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:38</v>
+        <v>2:22</v>
       </c>
       <c r="H41" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-28</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:40</v>
+        <v>3:53</v>
       </c>
       <c r="H42" t="str">
-        <v>Cannons</v>
+        <v>Roxette</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-28</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:57</v>
+        <v>2:28</v>
       </c>
       <c r="H43" t="str">
-        <v>Mimi Webb</v>
+        <v>Marcin</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-28</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:13</v>
+        <v>2:47</v>
       </c>
       <c r="H44" t="str">
-        <v>Jorja Smith</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-28</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:12</v>
+        <v>3:40</v>
       </c>
       <c r="H45" t="str">
-        <v>Sam Williams</v>
+        <v>Laufey</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-28</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:55</v>
+        <v>2:49</v>
       </c>
       <c r="H46" t="str">
-        <v>YUNGBLUD</v>
+        <v>Ava Max</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-28</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:51</v>
+        <v>4:49</v>
       </c>
       <c r="H47" t="str">
-        <v>Megan Moroney</v>
+        <v>U2</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-28</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:51</v>
+        <v>3:35</v>
       </c>
       <c r="H48" t="str">
-        <v>Nico Santos</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-28</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:24</v>
+        <v>2:59</v>
       </c>
       <c r="H49" t="str">
-        <v>REALITY CLUB</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-28</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>4:38</v>
       </c>
       <c r="H50" t="str">
-        <v>We Three</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-28</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:27</v>
+        <v>3:46</v>
       </c>
       <c r="H51" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-28</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:06</v>
+        <v>3:08</v>
       </c>
       <c r="H52" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-28</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:01</v>
+        <v>5:32</v>
       </c>
       <c r="H53" t="str">
-        <v>Peach PRC</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-28</v>
@@ -2427,10 +2427,10 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>5:38</v>
+        <v>4:39</v>
       </c>
       <c r="H54" t="str">
         <v>georgemichael</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-28</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:43</v>
+        <v>3:40</v>
       </c>
       <c r="H55" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-28</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:58</v>
+        <v>3:57</v>
       </c>
       <c r="H56" t="str">
-        <v>Catie Turner</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-28</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:13</v>
+        <v>2:27</v>
       </c>
       <c r="H57" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>070 Shake</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-28</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>5:48</v>
+        <v>4:49</v>
       </c>
       <c r="H58" t="str">
-        <v>U2</v>
+        <v>georgemichael</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-28</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:55</v>
+        <v>5:52</v>
       </c>
       <c r="H59" t="str">
-        <v>Lawrence</v>
+        <v>georgemichael</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-28</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:24</v>
+        <v>3:22</v>
       </c>
       <c r="H60" t="str">
-        <v>BUNT. Music</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-28</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:59</v>
+        <v>4:08</v>
       </c>
       <c r="H61" t="str">
-        <v>Bruno Mars</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-28</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:10</v>
+        <v>7:31</v>
       </c>
       <c r="H62" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-28</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:11</v>
+        <v>3:21</v>
       </c>
       <c r="H63" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-28</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:26</v>
+        <v>4:36</v>
       </c>
       <c r="H64" t="str">
-        <v>Neal Francis</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-28</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:35</v>
+        <v>5:06</v>
       </c>
       <c r="H65" t="str">
-        <v>mgk</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-28</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:09</v>
+        <v>4:17</v>
       </c>
       <c r="H66" t="str">
-        <v>Lola Young</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-28</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:11</v>
+        <v>3:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Holly Humberstone</v>
+        <v>georgemichael</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-28</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:01</v>
+        <v>4:50</v>
       </c>
       <c r="H68" t="str">
-        <v>The Vaccines</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-28</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:28</v>
+        <v>3:14</v>
       </c>
       <c r="H69" t="str">
-        <v>mgk</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-28</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:31</v>
+        <v>4:37</v>
       </c>
       <c r="H70" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-28</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:49</v>
+        <v>3:16</v>
       </c>
       <c r="H71" t="str">
-        <v>Mýa</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-28</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:03</v>
+        <v>4:22</v>
       </c>
       <c r="H72" t="str">
-        <v>Michael Bolton</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-28</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:59</v>
+        <v>4:40</v>
       </c>
       <c r="H73" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-28</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:41</v>
+        <v>3:02</v>
       </c>
       <c r="H74" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-28</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:59</v>
+        <v>3:12</v>
       </c>
       <c r="H75" t="str">
-        <v>ENHYPEN</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-28</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:59</v>
+        <v>3:38</v>
       </c>
       <c r="H76" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-28</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>7:48</v>
+        <v>4:40</v>
       </c>
       <c r="H77" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Cannons</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-28</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:10</v>
+        <v>2:57</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-28</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>5:57</v>
+        <v>2:13</v>
       </c>
       <c r="H79" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-28</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:25</v>
+        <v>4:12</v>
       </c>
       <c r="H80" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-28</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:19</v>
+        <v>2:55</v>
       </c>
       <c r="H81" t="str">
-        <v>Michael Bolton</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-28</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:38</v>
+        <v>3:51</v>
       </c>
       <c r="H82" t="str">
-        <v>mgk</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-28</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:05</v>
+        <v>2:51</v>
       </c>
       <c r="H83" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-28</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>5:46</v>
+        <v>3:24</v>
       </c>
       <c r="H84" t="str">
-        <v>Jacob Collier</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-28</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>4:11</v>
       </c>
       <c r="H85" t="str">
-        <v>Victor Ray</v>
+        <v>We Three</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-28</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>5:11</v>
+        <v>3:27</v>
       </c>
       <c r="H86" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-28</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:55</v>
+        <v>3:06</v>
       </c>
       <c r="H87" t="str">
-        <v>The Warning</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-28</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:54</v>
+        <v>3:01</v>
       </c>
       <c r="H88" t="str">
-        <v>The Offspring</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-28</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:01</v>
+        <v>5:38</v>
       </c>
       <c r="H89" t="str">
-        <v>Caitlyn Smith</v>
+        <v>georgemichael</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-28</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H90" t="str">
-        <v>HAUSER</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-28</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:43</v>
+        <v>2:58</v>
       </c>
       <c r="H91" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-28</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:53</v>
+        <v>4:13</v>
       </c>
       <c r="H92" t="str">
-        <v>Ultra Records</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-28</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:30</v>
+        <v>5:48</v>
       </c>
       <c r="H93" t="str">
-        <v>Anja Kotar</v>
+        <v>U2</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-28</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:37</v>
+        <v>3:55</v>
       </c>
       <c r="H94" t="str">
-        <v>Michael Bolton</v>
+        <v>Lawrence</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-28</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:10</v>
+        <v>5:24</v>
       </c>
       <c r="H95" t="str">
-        <v>Nothing But Thieves</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-28</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:06</v>
+        <v>4:59</v>
       </c>
       <c r="H96" t="str">
-        <v>Alan Walker</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-28</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:17</v>
+        <v>2:10</v>
       </c>
       <c r="H97" t="str">
-        <v>Bruno Mars</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-28</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H98" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-28</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>6:58</v>
+        <v>4:26</v>
       </c>
       <c r="H99" t="str">
-        <v>Eric Church</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-28</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:29</v>
+        <v>4:35</v>
       </c>
       <c r="H100" t="str">
-        <v>Meghan Trainor</v>
+        <v>mgk</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-28</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:14</v>
+        <v>2:09</v>
       </c>
       <c r="H101" t="str">
-        <v>Ally Salort</v>
+        <v>Lola Young</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:32</v>
@@ -515,7 +515,7 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:03</v>
@@ -553,7 +553,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:50</v>
@@ -591,7 +591,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:53</v>
@@ -629,7 +629,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:04</v>
@@ -1579,7 +1579,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>4:03</v>
@@ -1769,7 +1769,7 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:46</v>
@@ -1807,7 +1807,7 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:42</v>
@@ -1845,7 +1845,7 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:04</v>
@@ -1883,7 +1883,7 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>2:59</v>
@@ -2187,7 +2187,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:35</v>
@@ -2263,7 +2263,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:38</v>
@@ -2301,7 +2301,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:46</v>
@@ -2529,7 +2529,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>2:27</v>
@@ -2719,7 +2719,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>7:31</v>
@@ -2757,7 +2757,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:21</v>
@@ -3555,7 +3555,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:24</v>
@@ -3593,7 +3593,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>4:11</v>
@@ -3631,7 +3631,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:27</v>
@@ -3783,7 +3783,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>3:43</v>
@@ -3859,7 +3859,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>4:13</v>
@@ -3897,7 +3897,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>5:48</v>
@@ -3935,7 +3935,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:55</v>
@@ -4087,7 +4087,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:11</v>
@@ -4125,7 +4125,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:26</v>
@@ -4163,7 +4163,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>4:35</v>
@@ -4201,7 +4201,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>2:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-02-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:32</v>
@@ -2871,7 +2871,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B66" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>4:17</v>
@@ -3517,7 +3517,7 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>2:51</v>
@@ -3821,7 +3821,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>2:58</v>
